--- a/dicionario_dados/template1.xlsx
+++ b/dicionario_dados/template1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\codigos\projeto-bd2-satc\dicionario_dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e404f7af6d399db5/@SATC_Aula/202601/BDII/SEGUNDA/14 -Revisão da avaliação A2 e trabalho final com base em metodologias ativas de aprendizagem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEC94C6-ACA5-4C7C-8D61-130F0B6D9D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{5A897C1D-2E5E-4C7F-B782-B7F57F8C8B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48E1B00-F9F0-4016-B510-18FC140EE453}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8A75A3C3-1CC3-42DF-908E-18684CFF6B01}"/>
   </bookViews>
@@ -140,14 +140,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1" tint="0.14999847407452621"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1" tint="0.14999847407452621"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -200,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -208,6 +206,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -543,10 +542,13 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="15.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="3.85546875" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" customWidth="1"/>
-    <col min="8" max="8" width="37" customWidth="1"/>
+    <col min="1" max="3" width="15.5703125" style="3"/>
+    <col min="4" max="4" width="17.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="3"/>
+    <col min="6" max="6" width="3.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="37" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="15.5703125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -578,22 +580,22 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -618,20 +620,20 @@
         <v>10</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -640,78 +642,78 @@
         <v>15</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
@@ -721,79 +723,79 @@
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="6" t="s">
+      <c r="E14" s="9"/>
+      <c r="F14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="6" t="s">
+      <c r="E16" s="9"/>
+      <c r="F16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="21">
